--- a/SuppXLS/Scen_UC_CO2BND_UNDC.xlsx
+++ b/SuppXLS/Scen_UC_CO2BND_UNDC.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Veda\Veda_models\Demo_models\001_KHM_TIMES_20260609\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20550E68-0FBD-4C4D-8A00-B28AA80B1D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA62A312-9F32-495E-8262-561A8CA16C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UC_CO2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -83,9 +96,6 @@
   </si>
   <si>
     <t>UC_COMNET</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~0</t>
   </si>
   <si>
     <t>~UC_T:UC_RHSRTS</t>
@@ -131,6 +141,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -258,11 +271,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -272,7 +286,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -283,8 +296,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -777,45 +792,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="30.109375" customWidth="1"/>
-    <col min="5" max="6" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.109375" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="5" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -846,25 +861,22 @@
       <c r="K5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R5" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -875,22 +887,19 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="13">
         <v>38698.038611603704</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
       <c r="N6" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>2035</v>
@@ -901,291 +910,291 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="13">
         <v>44113.763969000276</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L8" s="8"/>
-      <c r="R8" s="11">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L8" s="7"/>
+      <c r="R8" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L9" s="8"/>
-      <c r="R9" s="11">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L9" s="7"/>
+      <c r="R9" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L10" s="8"/>
-      <c r="R10" s="11">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L10" s="7"/>
+      <c r="R10" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L11" s="13"/>
-      <c r="R11" s="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L11" s="12"/>
+      <c r="R11" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L12" s="8"/>
-      <c r="R12" s="11">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L12" s="7"/>
+      <c r="R12" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L13" s="8"/>
-      <c r="R13" s="11"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R14" s="11"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L13" s="7"/>
+      <c r="R13" s="10"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R14" s="10"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="12">
+        <v>23</v>
+      </c>
+      <c r="E24" s="11">
         <v>2021</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <v>2022</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>2025</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <v>2030</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <v>2035</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="11">
         <v>2040</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="11">
         <v>2045</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="11">
         <v>2050</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="8">
+        <v>29</v>
+      </c>
+      <c r="E25" s="7">
         <v>212.996312980043</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="7">
         <v>215.126933673108</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="7">
         <v>219.45021741073</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>208.99178617328499</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="7">
         <v>215.36232794977801</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="7">
         <v>299.56219780110598</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <v>438.66276574882198</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="7">
         <v>614.47419912945702</v>
       </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="8">
+        <v>30</v>
+      </c>
+      <c r="E26" s="7">
         <v>415.09356099436798</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="7">
         <v>624.84542887571195</v>
       </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="8">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7">
         <v>4376.8518750000003</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="7">
         <v>4267.4305781249996</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="7">
         <v>8137.7181190741803</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="7">
         <v>11693.390132928</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="7">
         <v>14602.186331349199</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="7">
         <v>19125.548650918201</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="7">
         <v>20895.687152768402</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="7">
         <v>22832.5364037578</v>
       </c>
-      <c r="M27" s="8"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="8">
+        <v>31</v>
+      </c>
+      <c r="E28" s="7">
         <v>2655.2364891120001</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="7">
         <v>2604.7174731884402</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="7">
         <v>2452.8531742294499</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="7">
         <v>2428.2953689283499</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="7">
         <v>2558.4322615832202</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="7">
         <v>2241.06789690606</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="7">
         <v>2278.1724800616398</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="7">
         <v>2351.4438346757902</v>
       </c>
-      <c r="M28" s="8"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="8">
+        <v>26</v>
+      </c>
+      <c r="E29" s="7">
         <v>677.38136214383997</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="8">
+        <v>25</v>
+      </c>
+      <c r="E30" s="7">
         <v>3629.4944045064599</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="7">
         <v>5286.0414232104004</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="7">
         <v>5592.5571705351804</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="7">
         <v>4855.1326647040896</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="7">
         <v>4913.7843375759503</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="7">
         <v>4958.9207832316597</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="7">
         <v>4717.3792537071504</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="7">
         <v>5341.4174679000098</v>
       </c>
-      <c r="M30" s="8"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M30" s="7"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32">
         <f>E35</f>
@@ -1197,65 +1206,65 @@
       <c r="G32">
         <v>31095.369296976274</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="7">
         <v>38698.038611603704</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="7">
         <v>44113.763969000276</v>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-    </row>
-    <row r="33" spans="4:19" x14ac:dyDescent="0.3">
-      <c r="E33" s="12">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="E33" s="11">
         <v>2021</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="11">
         <v>2022</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>2023</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>2024</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="11">
         <v>2025</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="11">
         <v>2026</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="11">
         <v>2027</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="11">
         <v>2028</v>
       </c>
-      <c r="M33" s="12">
+      <c r="M33" s="11">
         <v>2029</v>
       </c>
-      <c r="N33" s="12">
+      <c r="N33" s="11">
         <v>2030</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O33" s="11">
         <v>2031</v>
       </c>
-      <c r="P33" s="12">
+      <c r="P33" s="11">
         <v>2032</v>
       </c>
-      <c r="Q33" s="12">
+      <c r="Q33" s="11">
         <v>2033</v>
       </c>
-      <c r="R33" s="12">
+      <c r="R33" s="11">
         <v>2034</v>
       </c>
-      <c r="S33" s="12">
+      <c r="S33" s="11">
         <v>2035</v>
       </c>
     </row>
-    <row r="34" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E34">
         <v>20.633521014270102</v>
       </c>
@@ -1302,7 +1311,7 @@
         <v>44.113763969000274</v>
       </c>
     </row>
-    <row r="35" spans="4:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D35">
         <f>10^3</f>
         <v>1000</v>

--- a/SuppXLS/Scen_UC_CO2BND_UNDC.xlsx
+++ b/SuppXLS/Scen_UC_CO2BND_UNDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA62A312-9F32-495E-8262-561A8CA16C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05681B7-9EC4-4300-B883-7148D089BB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UC_CO2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>DemoS_010</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
   </si>
 </sst>
 </file>
@@ -278,7 +281,7 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -297,6 +300,7 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
@@ -864,6 +868,9 @@
       <c r="L5" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="M5" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="N5" s="4" t="s">
         <v>11</v>
       </c>
@@ -889,6 +896,9 @@
       </c>
       <c r="L6" s="13">
         <v>38698.038611603704</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
       <c r="N6" t="s">
         <v>19</v>
